--- a/virtual-physics-lab/app/dl/ACJC_Q3f_sand_dataset.xlsx
+++ b/virtual-physics-lab/app/dl/ACJC_Q3f_sand_dataset.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,6 +100,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -668,685 +669,685 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>19.99</v>
       </c>
-      <c r="C6" s="6" t="n"/>
+      <c r="C6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>19.13</v>
       </c>
-      <c r="C7" s="6" t="n"/>
+      <c r="C7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>18.36</v>
       </c>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>17.36</v>
       </c>
-      <c r="C9" s="6" t="n"/>
+      <c r="C9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>16.64</v>
       </c>
-      <c r="C10" s="6" t="n"/>
+      <c r="C10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>15.89</v>
       </c>
-      <c r="C11" s="6" t="n"/>
+      <c r="C11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>15.12</v>
       </c>
-      <c r="C12" s="6" t="n"/>
+      <c r="C12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>14.46</v>
       </c>
-      <c r="C13" s="6" t="n"/>
+      <c r="C13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>13.92</v>
       </c>
-      <c r="C14" s="6" t="n"/>
+      <c r="C14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>13.25</v>
       </c>
-      <c r="C15" s="6" t="n"/>
+      <c r="C15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>12.52</v>
       </c>
-      <c r="C16" s="6" t="n"/>
+      <c r="C16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>12.07</v>
       </c>
-      <c r="C17" s="6" t="n"/>
+      <c r="C17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="6" t="n">
         <v>11.5</v>
       </c>
-      <c r="C18" s="6" t="n"/>
+      <c r="C18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>10.97</v>
       </c>
-      <c r="C19" s="6" t="n"/>
+      <c r="C19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>10.43</v>
       </c>
-      <c r="C20" s="6" t="n"/>
+      <c r="C20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="6" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="C21" s="6" t="n"/>
+      <c r="C21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>9.56</v>
       </c>
-      <c r="C22" s="6" t="n"/>
+      <c r="C22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>9.1</v>
       </c>
-      <c r="C23" s="6" t="n"/>
+      <c r="C23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="6" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="C24" s="6" t="n"/>
+      <c r="C24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="6" t="n">
         <v>8.32</v>
       </c>
-      <c r="C25" s="6" t="n"/>
+      <c r="C25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="6" t="n">
         <v>7.96</v>
       </c>
-      <c r="C26" s="6" t="n"/>
+      <c r="C26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>7.6</v>
       </c>
-      <c r="C27" s="6" t="n"/>
+      <c r="C27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="6" t="n">
         <v>7.25</v>
       </c>
-      <c r="C28" s="6" t="n"/>
+      <c r="C28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="6" t="n">
         <v>6.89</v>
       </c>
-      <c r="C29" s="6" t="n"/>
+      <c r="C29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>6.55</v>
       </c>
-      <c r="C30" s="6" t="n"/>
+      <c r="C30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="6" t="n">
         <v>6.31</v>
       </c>
-      <c r="C31" s="6" t="n"/>
+      <c r="C31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="6" t="n">
         <v>6.04</v>
       </c>
-      <c r="C32" s="6" t="n"/>
+      <c r="C32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="6" t="n">
         <v>5.77</v>
       </c>
-      <c r="C33" s="6" t="n"/>
+      <c r="C33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="6" t="n">
         <v>5.48</v>
       </c>
-      <c r="C34" s="6" t="n"/>
+      <c r="C34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="6" t="n">
         <v>5.23</v>
       </c>
-      <c r="C35" s="6" t="n"/>
+      <c r="C35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="6" t="n">
         <v>5.01</v>
       </c>
-      <c r="C36" s="6" t="n"/>
+      <c r="C36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="6" t="n">
         <v>4.79</v>
       </c>
-      <c r="C37" s="6" t="n"/>
+      <c r="C37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="6" t="n">
         <v>4.53</v>
       </c>
-      <c r="C38" s="6" t="n"/>
+      <c r="C38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="6" t="n">
         <v>4.34</v>
       </c>
-      <c r="C39" s="6" t="n"/>
+      <c r="C39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="6" t="n">
         <v>4.15</v>
       </c>
-      <c r="C40" s="6" t="n"/>
+      <c r="C40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="6" t="n">
         <v>3.97</v>
       </c>
-      <c r="C41" s="6" t="n"/>
+      <c r="C41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="6" t="n">
         <v>3.78</v>
       </c>
-      <c r="C42" s="6" t="n"/>
+      <c r="C42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="6" t="n">
         <v>3.64</v>
       </c>
-      <c r="C43" s="6" t="n"/>
+      <c r="C43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B44" s="6" t="n">
         <v>3.46</v>
       </c>
-      <c r="C44" s="6" t="n"/>
+      <c r="C44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B45" s="6" t="n">
         <v>3.29</v>
       </c>
-      <c r="C45" s="6" t="n"/>
+      <c r="C45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="6" t="n">
         <v>3.17</v>
       </c>
-      <c r="C46" s="6" t="n"/>
+      <c r="C46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B47" s="6" t="n">
         <v>3.01</v>
       </c>
-      <c r="C47" s="6" t="n"/>
+      <c r="C47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="6" t="n">
         <v>2.89</v>
       </c>
-      <c r="C48" s="6" t="n"/>
+      <c r="C48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="6" t="n">
         <v>2.74</v>
       </c>
-      <c r="C49" s="6" t="n"/>
+      <c r="C49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="6" t="n">
         <v>2.61</v>
       </c>
-      <c r="C50" s="6" t="n"/>
+      <c r="C50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="C51" s="6" t="n"/>
+      <c r="C51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B52" s="6" t="n">
         <v>2.4</v>
       </c>
-      <c r="C52" s="6" t="n"/>
+      <c r="C52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B53" s="5" t="n">
+      <c r="B53" s="6" t="n">
         <v>2.27</v>
       </c>
-      <c r="C53" s="6" t="n"/>
+      <c r="C53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="B54" s="5" t="n">
+      <c r="B54" s="6" t="n">
         <v>2.19</v>
       </c>
-      <c r="C54" s="6" t="n"/>
+      <c r="C54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B55" s="5" t="n">
+      <c r="B55" s="6" t="n">
         <v>2.08</v>
       </c>
-      <c r="C55" s="6" t="n"/>
+      <c r="C55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B56" s="6" t="n">
         <v>1.99</v>
       </c>
-      <c r="C56" s="6" t="n"/>
+      <c r="C56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="B57" s="5" t="n">
+      <c r="B57" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="C57" s="6" t="n"/>
+      <c r="C57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="B58" s="5" t="n">
+      <c r="B58" s="6" t="n">
         <v>1.8</v>
       </c>
-      <c r="C58" s="6" t="n"/>
+      <c r="C58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="B59" s="5" t="n">
+      <c r="B59" s="6" t="n">
         <v>1.73</v>
       </c>
-      <c r="C59" s="6" t="n"/>
+      <c r="C59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
         <v>108</v>
       </c>
-      <c r="B60" s="5" t="n">
+      <c r="B60" s="6" t="n">
         <v>1.64</v>
       </c>
-      <c r="C60" s="6" t="n"/>
+      <c r="C60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="B61" s="5" t="n">
+      <c r="B61" s="6" t="n">
         <v>1.57</v>
       </c>
-      <c r="C61" s="6" t="n"/>
+      <c r="C61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="B62" s="5" t="n">
+      <c r="B62" s="6" t="n">
         <v>1.51</v>
       </c>
-      <c r="C62" s="6" t="n"/>
+      <c r="C62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="B63" s="5" t="n">
+      <c r="B63" s="6" t="n">
         <v>1.43</v>
       </c>
-      <c r="C63" s="6" t="n"/>
+      <c r="C63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
         <v>116</v>
       </c>
-      <c r="B64" s="5" t="n">
+      <c r="B64" s="6" t="n">
         <v>1.37</v>
       </c>
-      <c r="C64" s="6" t="n"/>
+      <c r="C64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
         <v>118</v>
       </c>
-      <c r="B65" s="5" t="n">
+      <c r="B65" s="6" t="n">
         <v>1.31</v>
       </c>
-      <c r="C65" s="6" t="n"/>
+      <c r="C65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="B66" s="5" t="n">
+      <c r="B66" s="6" t="n">
         <v>1.24</v>
       </c>
-      <c r="C66" s="6" t="n"/>
+      <c r="C66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
         <v>122</v>
       </c>
-      <c r="B67" s="5" t="n">
+      <c r="B67" s="6" t="n">
         <v>1.19</v>
       </c>
-      <c r="C67" s="6" t="n"/>
+      <c r="C67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
         <v>124</v>
       </c>
-      <c r="B68" s="5" t="n">
+      <c r="B68" s="6" t="n">
         <v>1.14</v>
       </c>
-      <c r="C68" s="6" t="n"/>
+      <c r="C68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="B69" s="5" t="n">
+      <c r="B69" s="6" t="n">
         <v>1.09</v>
       </c>
-      <c r="C69" s="6" t="n"/>
+      <c r="C69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
         <v>128</v>
       </c>
-      <c r="B70" s="5" t="n">
+      <c r="B70" s="6" t="n">
         <v>1.04</v>
       </c>
-      <c r="C70" s="6" t="n"/>
+      <c r="C70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B71" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C71" s="6" t="n"/>
+      <c r="C71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="B72" s="5" t="n">
+      <c r="B72" s="6" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="C72" s="6" t="n"/>
+      <c r="C72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
         <v>134</v>
       </c>
-      <c r="B73" s="5" t="n">
+      <c r="B73" s="6" t="n">
         <v>0.91</v>
       </c>
-      <c r="C73" s="6" t="n"/>
+      <c r="C73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
         <v>136</v>
       </c>
-      <c r="B74" s="5" t="n">
+      <c r="B74" s="6" t="n">
         <v>0.86</v>
       </c>
-      <c r="C74" s="6" t="n"/>
+      <c r="C74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
         <v>138</v>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B75" s="6" t="n">
         <v>0.83</v>
       </c>
-      <c r="C75" s="6" t="n"/>
+      <c r="C75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="B76" s="5" t="n">
+      <c r="B76" s="6" t="n">
         <v>0.78</v>
       </c>
-      <c r="C76" s="6" t="n"/>
+      <c r="C76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
         <v>142</v>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B77" s="6" t="n">
         <v>0.75</v>
       </c>
-      <c r="C77" s="6" t="n"/>
+      <c r="C77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
         <v>144</v>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B78" s="6" t="n">
         <v>0.72</v>
       </c>
-      <c r="C78" s="6" t="n"/>
+      <c r="C78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
         <v>146</v>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B79" s="6" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="C79" s="6" t="n"/>
+      <c r="C79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
         <v>148</v>
       </c>
-      <c r="B80" s="5" t="n">
+      <c r="B80" s="6" t="n">
         <v>0.66</v>
       </c>
-      <c r="C80" s="6" t="n"/>
+      <c r="C80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="B81" s="5" t="n">
+      <c r="B81" s="6" t="n">
         <v>0.63</v>
       </c>
-      <c r="C81" s="6" t="n"/>
+      <c r="C81" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1420,10 +1421,10 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>19.99</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <f>LN(B6)</f>
         <v/>
       </c>
@@ -1432,7 +1433,7 @@
           <t>k = −gradient</t>
         </is>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f>-SLOPE(C6:C81,A6:A81)</f>
         <v/>
       </c>
@@ -1446,10 +1447,10 @@
       <c r="A7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>19.13</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <f>LN(B7)</f>
         <v/>
       </c>
@@ -1458,7 +1459,7 @@
           <t>ln2 / k</t>
         </is>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <f>LN(2)/-SLOPE(C6:C81,A6:A81)</f>
         <v/>
       </c>
@@ -1472,10 +1473,10 @@
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>18.36</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f>LN(B8)</f>
         <v/>
       </c>
@@ -1484,10 +1485,10 @@
       <c r="A9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>17.36</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <f>LN(B9)</f>
         <v/>
       </c>
@@ -1496,10 +1497,10 @@
       <c r="A10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>16.64</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <f>LN(B10)</f>
         <v/>
       </c>
@@ -1508,10 +1509,10 @@
       <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>15.89</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <f>LN(B11)</f>
         <v/>
       </c>
@@ -1520,10 +1521,10 @@
       <c r="A12" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>15.12</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <f>LN(B12)</f>
         <v/>
       </c>
@@ -1532,10 +1533,10 @@
       <c r="A13" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>14.46</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <f>LN(B13)</f>
         <v/>
       </c>
@@ -1544,10 +1545,10 @@
       <c r="A14" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>13.92</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="8">
         <f>LN(B14)</f>
         <v/>
       </c>
@@ -1556,10 +1557,10 @@
       <c r="A15" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>13.25</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <f>LN(B15)</f>
         <v/>
       </c>
@@ -1568,10 +1569,10 @@
       <c r="A16" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>12.52</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <f>LN(B16)</f>
         <v/>
       </c>
@@ -1580,10 +1581,10 @@
       <c r="A17" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>12.07</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <f>LN(B17)</f>
         <v/>
       </c>
@@ -1592,10 +1593,10 @@
       <c r="A18" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="6" t="n">
         <v>11.5</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <f>LN(B18)</f>
         <v/>
       </c>
@@ -1604,10 +1605,10 @@
       <c r="A19" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>10.97</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <f>LN(B19)</f>
         <v/>
       </c>
@@ -1616,10 +1617,10 @@
       <c r="A20" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>10.43</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <f>LN(B20)</f>
         <v/>
       </c>
@@ -1628,10 +1629,10 @@
       <c r="A21" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="6" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <f>LN(B21)</f>
         <v/>
       </c>
@@ -1640,10 +1641,10 @@
       <c r="A22" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>9.56</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <f>LN(B22)</f>
         <v/>
       </c>
@@ -1652,10 +1653,10 @@
       <c r="A23" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>9.1</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <f>LN(B23)</f>
         <v/>
       </c>
@@ -1664,10 +1665,10 @@
       <c r="A24" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="6" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="8">
         <f>LN(B24)</f>
         <v/>
       </c>
@@ -1676,10 +1677,10 @@
       <c r="A25" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="6" t="n">
         <v>8.32</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="8">
         <f>LN(B25)</f>
         <v/>
       </c>
@@ -1688,10 +1689,10 @@
       <c r="A26" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="6" t="n">
         <v>7.96</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="8">
         <f>LN(B26)</f>
         <v/>
       </c>
@@ -1700,10 +1701,10 @@
       <c r="A27" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>7.6</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="8">
         <f>LN(B27)</f>
         <v/>
       </c>
@@ -1712,10 +1713,10 @@
       <c r="A28" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="6" t="n">
         <v>7.25</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="8">
         <f>LN(B28)</f>
         <v/>
       </c>
@@ -1724,10 +1725,10 @@
       <c r="A29" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="6" t="n">
         <v>6.89</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="8">
         <f>LN(B29)</f>
         <v/>
       </c>
@@ -1736,10 +1737,10 @@
       <c r="A30" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>6.55</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="8">
         <f>LN(B30)</f>
         <v/>
       </c>
@@ -1748,10 +1749,10 @@
       <c r="A31" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="6" t="n">
         <v>6.31</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="8">
         <f>LN(B31)</f>
         <v/>
       </c>
@@ -1760,10 +1761,10 @@
       <c r="A32" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="6" t="n">
         <v>6.04</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="8">
         <f>LN(B32)</f>
         <v/>
       </c>
@@ -1772,10 +1773,10 @@
       <c r="A33" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="6" t="n">
         <v>5.77</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="8">
         <f>LN(B33)</f>
         <v/>
       </c>
@@ -1784,10 +1785,10 @@
       <c r="A34" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="6" t="n">
         <v>5.48</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="8">
         <f>LN(B34)</f>
         <v/>
       </c>
@@ -1796,10 +1797,10 @@
       <c r="A35" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="6" t="n">
         <v>5.23</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="8">
         <f>LN(B35)</f>
         <v/>
       </c>
@@ -1808,10 +1809,10 @@
       <c r="A36" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="6" t="n">
         <v>5.01</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="8">
         <f>LN(B36)</f>
         <v/>
       </c>
@@ -1820,10 +1821,10 @@
       <c r="A37" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="6" t="n">
         <v>4.79</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="8">
         <f>LN(B37)</f>
         <v/>
       </c>
@@ -1832,10 +1833,10 @@
       <c r="A38" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="6" t="n">
         <v>4.53</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="8">
         <f>LN(B38)</f>
         <v/>
       </c>
@@ -1844,10 +1845,10 @@
       <c r="A39" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="6" t="n">
         <v>4.34</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="8">
         <f>LN(B39)</f>
         <v/>
       </c>
@@ -1856,10 +1857,10 @@
       <c r="A40" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="6" t="n">
         <v>4.15</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="8">
         <f>LN(B40)</f>
         <v/>
       </c>
@@ -1868,10 +1869,10 @@
       <c r="A41" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="6" t="n">
         <v>3.97</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="8">
         <f>LN(B41)</f>
         <v/>
       </c>
@@ -1880,10 +1881,10 @@
       <c r="A42" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="6" t="n">
         <v>3.78</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="8">
         <f>LN(B42)</f>
         <v/>
       </c>
@@ -1892,10 +1893,10 @@
       <c r="A43" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="6" t="n">
         <v>3.64</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="8">
         <f>LN(B43)</f>
         <v/>
       </c>
@@ -1904,10 +1905,10 @@
       <c r="A44" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B44" s="6" t="n">
         <v>3.46</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="8">
         <f>LN(B44)</f>
         <v/>
       </c>
@@ -1916,10 +1917,10 @@
       <c r="A45" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B45" s="6" t="n">
         <v>3.29</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="8">
         <f>LN(B45)</f>
         <v/>
       </c>
@@ -1928,10 +1929,10 @@
       <c r="A46" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="6" t="n">
         <v>3.17</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="8">
         <f>LN(B46)</f>
         <v/>
       </c>
@@ -1940,10 +1941,10 @@
       <c r="A47" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B47" s="6" t="n">
         <v>3.01</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="8">
         <f>LN(B47)</f>
         <v/>
       </c>
@@ -1952,10 +1953,10 @@
       <c r="A48" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="6" t="n">
         <v>2.89</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C48" s="8">
         <f>LN(B48)</f>
         <v/>
       </c>
@@ -1964,10 +1965,10 @@
       <c r="A49" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="6" t="n">
         <v>2.74</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="8">
         <f>LN(B49)</f>
         <v/>
       </c>
@@ -1976,10 +1977,10 @@
       <c r="A50" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="6" t="n">
         <v>2.61</v>
       </c>
-      <c r="C50" s="7">
+      <c r="C50" s="8">
         <f>LN(B50)</f>
         <v/>
       </c>
@@ -1988,10 +1989,10 @@
       <c r="A51" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C51" s="8">
         <f>LN(B51)</f>
         <v/>
       </c>
@@ -2000,10 +2001,10 @@
       <c r="A52" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B52" s="6" t="n">
         <v>2.4</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C52" s="8">
         <f>LN(B52)</f>
         <v/>
       </c>
@@ -2012,10 +2013,10 @@
       <c r="A53" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B53" s="5" t="n">
+      <c r="B53" s="6" t="n">
         <v>2.27</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C53" s="8">
         <f>LN(B53)</f>
         <v/>
       </c>
@@ -2024,10 +2025,10 @@
       <c r="A54" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="B54" s="5" t="n">
+      <c r="B54" s="6" t="n">
         <v>2.19</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C54" s="8">
         <f>LN(B54)</f>
         <v/>
       </c>
@@ -2036,10 +2037,10 @@
       <c r="A55" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B55" s="5" t="n">
+      <c r="B55" s="6" t="n">
         <v>2.08</v>
       </c>
-      <c r="C55" s="7">
+      <c r="C55" s="8">
         <f>LN(B55)</f>
         <v/>
       </c>
@@ -2048,10 +2049,10 @@
       <c r="A56" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B56" s="6" t="n">
         <v>1.99</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="8">
         <f>LN(B56)</f>
         <v/>
       </c>
@@ -2060,10 +2061,10 @@
       <c r="A57" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="B57" s="5" t="n">
+      <c r="B57" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="C57" s="7">
+      <c r="C57" s="8">
         <f>LN(B57)</f>
         <v/>
       </c>
@@ -2072,10 +2073,10 @@
       <c r="A58" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="B58" s="5" t="n">
+      <c r="B58" s="6" t="n">
         <v>1.8</v>
       </c>
-      <c r="C58" s="7">
+      <c r="C58" s="8">
         <f>LN(B58)</f>
         <v/>
       </c>
@@ -2084,10 +2085,10 @@
       <c r="A59" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="B59" s="5" t="n">
+      <c r="B59" s="6" t="n">
         <v>1.73</v>
       </c>
-      <c r="C59" s="7">
+      <c r="C59" s="8">
         <f>LN(B59)</f>
         <v/>
       </c>
@@ -2096,10 +2097,10 @@
       <c r="A60" s="5" t="n">
         <v>108</v>
       </c>
-      <c r="B60" s="5" t="n">
+      <c r="B60" s="6" t="n">
         <v>1.64</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="8">
         <f>LN(B60)</f>
         <v/>
       </c>
@@ -2108,10 +2109,10 @@
       <c r="A61" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="B61" s="5" t="n">
+      <c r="B61" s="6" t="n">
         <v>1.57</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="8">
         <f>LN(B61)</f>
         <v/>
       </c>
@@ -2120,10 +2121,10 @@
       <c r="A62" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="B62" s="5" t="n">
+      <c r="B62" s="6" t="n">
         <v>1.51</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C62" s="8">
         <f>LN(B62)</f>
         <v/>
       </c>
@@ -2132,10 +2133,10 @@
       <c r="A63" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="B63" s="5" t="n">
+      <c r="B63" s="6" t="n">
         <v>1.43</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C63" s="8">
         <f>LN(B63)</f>
         <v/>
       </c>
@@ -2144,10 +2145,10 @@
       <c r="A64" s="5" t="n">
         <v>116</v>
       </c>
-      <c r="B64" s="5" t="n">
+      <c r="B64" s="6" t="n">
         <v>1.37</v>
       </c>
-      <c r="C64" s="7">
+      <c r="C64" s="8">
         <f>LN(B64)</f>
         <v/>
       </c>
@@ -2156,10 +2157,10 @@
       <c r="A65" s="5" t="n">
         <v>118</v>
       </c>
-      <c r="B65" s="5" t="n">
+      <c r="B65" s="6" t="n">
         <v>1.31</v>
       </c>
-      <c r="C65" s="7">
+      <c r="C65" s="8">
         <f>LN(B65)</f>
         <v/>
       </c>
@@ -2168,10 +2169,10 @@
       <c r="A66" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="B66" s="5" t="n">
+      <c r="B66" s="6" t="n">
         <v>1.24</v>
       </c>
-      <c r="C66" s="7">
+      <c r="C66" s="8">
         <f>LN(B66)</f>
         <v/>
       </c>
@@ -2180,10 +2181,10 @@
       <c r="A67" s="5" t="n">
         <v>122</v>
       </c>
-      <c r="B67" s="5" t="n">
+      <c r="B67" s="6" t="n">
         <v>1.19</v>
       </c>
-      <c r="C67" s="7">
+      <c r="C67" s="8">
         <f>LN(B67)</f>
         <v/>
       </c>
@@ -2192,10 +2193,10 @@
       <c r="A68" s="5" t="n">
         <v>124</v>
       </c>
-      <c r="B68" s="5" t="n">
+      <c r="B68" s="6" t="n">
         <v>1.14</v>
       </c>
-      <c r="C68" s="7">
+      <c r="C68" s="8">
         <f>LN(B68)</f>
         <v/>
       </c>
@@ -2204,10 +2205,10 @@
       <c r="A69" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="B69" s="5" t="n">
+      <c r="B69" s="6" t="n">
         <v>1.09</v>
       </c>
-      <c r="C69" s="7">
+      <c r="C69" s="8">
         <f>LN(B69)</f>
         <v/>
       </c>
@@ -2216,10 +2217,10 @@
       <c r="A70" s="5" t="n">
         <v>128</v>
       </c>
-      <c r="B70" s="5" t="n">
+      <c r="B70" s="6" t="n">
         <v>1.04</v>
       </c>
-      <c r="C70" s="7">
+      <c r="C70" s="8">
         <f>LN(B70)</f>
         <v/>
       </c>
@@ -2228,10 +2229,10 @@
       <c r="A71" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B71" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C71" s="7">
+      <c r="C71" s="8">
         <f>LN(B71)</f>
         <v/>
       </c>
@@ -2240,10 +2241,10 @@
       <c r="A72" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="B72" s="5" t="n">
+      <c r="B72" s="6" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="C72" s="7">
+      <c r="C72" s="8">
         <f>LN(B72)</f>
         <v/>
       </c>
@@ -2252,10 +2253,10 @@
       <c r="A73" s="5" t="n">
         <v>134</v>
       </c>
-      <c r="B73" s="5" t="n">
+      <c r="B73" s="6" t="n">
         <v>0.91</v>
       </c>
-      <c r="C73" s="7">
+      <c r="C73" s="8">
         <f>LN(B73)</f>
         <v/>
       </c>
@@ -2264,10 +2265,10 @@
       <c r="A74" s="5" t="n">
         <v>136</v>
       </c>
-      <c r="B74" s="5" t="n">
+      <c r="B74" s="6" t="n">
         <v>0.86</v>
       </c>
-      <c r="C74" s="7">
+      <c r="C74" s="8">
         <f>LN(B74)</f>
         <v/>
       </c>
@@ -2276,10 +2277,10 @@
       <c r="A75" s="5" t="n">
         <v>138</v>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B75" s="6" t="n">
         <v>0.83</v>
       </c>
-      <c r="C75" s="7">
+      <c r="C75" s="8">
         <f>LN(B75)</f>
         <v/>
       </c>
@@ -2288,10 +2289,10 @@
       <c r="A76" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="B76" s="5" t="n">
+      <c r="B76" s="6" t="n">
         <v>0.78</v>
       </c>
-      <c r="C76" s="7">
+      <c r="C76" s="8">
         <f>LN(B76)</f>
         <v/>
       </c>
@@ -2300,10 +2301,10 @@
       <c r="A77" s="5" t="n">
         <v>142</v>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B77" s="6" t="n">
         <v>0.75</v>
       </c>
-      <c r="C77" s="7">
+      <c r="C77" s="8">
         <f>LN(B77)</f>
         <v/>
       </c>
@@ -2312,10 +2313,10 @@
       <c r="A78" s="5" t="n">
         <v>144</v>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B78" s="6" t="n">
         <v>0.72</v>
       </c>
-      <c r="C78" s="7">
+      <c r="C78" s="8">
         <f>LN(B78)</f>
         <v/>
       </c>
@@ -2324,10 +2325,10 @@
       <c r="A79" s="5" t="n">
         <v>146</v>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B79" s="6" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="C79" s="7">
+      <c r="C79" s="8">
         <f>LN(B79)</f>
         <v/>
       </c>
@@ -2336,10 +2337,10 @@
       <c r="A80" s="5" t="n">
         <v>148</v>
       </c>
-      <c r="B80" s="5" t="n">
+      <c r="B80" s="6" t="n">
         <v>0.66</v>
       </c>
-      <c r="C80" s="7">
+      <c r="C80" s="8">
         <f>LN(B80)</f>
         <v/>
       </c>
@@ -2348,10 +2349,10 @@
       <c r="A81" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="B81" s="5" t="n">
+      <c r="B81" s="6" t="n">
         <v>0.63</v>
       </c>
-      <c r="C81" s="7">
+      <c r="C81" s="8">
         <f>LN(B81)</f>
         <v/>
       </c>
